--- a/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-other-observations-codes.xlsx
+++ b/r4-JoanneumResearch-PreNUDGE-AppData-main/ValueSet-prenudge-other-observations-codes.xlsx
@@ -61,7 +61,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-26T07:28:06+00:00</t>
+    <t>2026-10-21T09:39:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
